--- a/server/excel/release/rune.xlsx
+++ b/server/excel/release/rune.xlsx
@@ -616,7 +616,7 @@
     <t xml:space="preserve">估值</t>
   </si>
   <si>
-    <t xml:space="preserve">Tửu Túy Quyền</t>
+    <t xml:space="preserve">Haki cấp 1</t>
   </si>
   <si>
     <t xml:space="preserve">Cường hóa tướng</t>
@@ -640,7 +640,7 @@
     <t xml:space="preserve">3:100004:60</t>
   </si>
   <si>
-    <t xml:space="preserve">Thái Cực Kiếm</t>
+    <t xml:space="preserve">Haki cấp 2</t>
   </si>
   <si>
     <t xml:space="preserve">1:10000</t>
@@ -658,7 +658,7 @@
     <t xml:space="preserve">3:100004:300</t>
   </si>
   <si>
-    <t xml:space="preserve">Cửu Âm Công</t>
+    <t xml:space="preserve">Haki cấp 3</t>
   </si>
   <si>
     <t xml:space="preserve">1,1:3000#1,2:3000#2:4000</t>
@@ -679,7 +679,7 @@
     <t xml:space="preserve">3:100004:1500</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhất Chỉ Công</t>
+    <t xml:space="preserve">Haki cấp S</t>
   </si>
   <si>
     <t xml:space="preserve">3,2:3000#3,1:3000#2,2:2000#3,2:2000</t>
@@ -706,7 +706,7 @@
     <t xml:space="preserve">3:100004:7500</t>
   </si>
   <si>
-    <t xml:space="preserve">Cửu Dương Công</t>
+    <t xml:space="preserve">Haki cấp SS</t>
   </si>
   <si>
     <t xml:space="preserve">5,6</t>
@@ -733,7 +733,7 @@
     <t xml:space="preserve">3:100004:37500</t>
   </si>
   <si>
-    <t xml:space="preserve">Thiên Ngoại Phi Tiên</t>
+    <t xml:space="preserve">Haki cấp SSS</t>
   </si>
   <si>
     <t xml:space="preserve">2#1</t>
@@ -853,7 +853,7 @@
     <t xml:space="preserve">3:100004:10000#0:0:2000000</t>
   </si>
   <si>
-    <t xml:space="preserve">Sách thiên phú</t>
+    <t xml:space="preserve">Năng Lượng Haki</t>
   </si>
   <si>
     <t xml:space="preserve">技能等级组合</t>

--- a/server/excel/release/rune.xlsx
+++ b/server/excel/release/rune.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="符文属性" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="符文基础" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="符文技能特殊洗练" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="符文技能" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="符文技能评分" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="符文锻造" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="自定义符文道具" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sheet1" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="符文配置对照" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文属性" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文基础" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文技能特殊洗练" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文技能" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文技能评分" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文锻造" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自定义符文道具" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="符文配置对照" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,10 +625,10 @@
     <t xml:space="preserve">Tỉ ấn</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;24671&gt; Chủng loại tính &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2406 [ Hổ phương ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nhưng từ trở xuống thuộc tính cơ sở bên trong ngẫu nhiên nhận được &lt;24671&gt; Loại &lt;br&gt;&lt;2405 【 Công kích 】【 Sinh mệnh 】【 Phòng ngự 】【 Tốc độ 】&gt;</t>
+    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;2467 1&gt; Chủng loại tính &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2406 [ Hổ phương ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhưng từ trở xuống thuộc tính cơ sở bên trong ngẫu nhiên nhận được &lt;2467 1&gt; Loại &lt;br&gt;&lt;2405 【 Công kích 】【 Sinh mệnh 】【 Phòng ngự 】【 Tốc độ 】&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">17#24#34</t>
@@ -646,7 +646,7 @@
     <t xml:space="preserve">1:10000</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;24671&gt; Chủng loại tính, &lt;2467 1&gt; Cái sơ cấp kỹ năng &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2407[ Bạch Trạch ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
+    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;2467 1&gt; Chủng loại tính, &lt;2467 1&gt; Cái sơ cấp kỹ năng &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2407[ Bạch Trạch ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
   </si>
   <si>
     <t xml:space="preserve">1.&lt;2405【 Sơ cấp kỹ năng 】&gt;&lt;br&gt;&lt;br&gt; Ngẫu nhiên nhận được &lt;2467 1&gt; Loại sơ cấp kỹ năng bị động</t>
@@ -667,7 +667,7 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;24671&gt; Chủng loại tính, &lt;2467 1-2&gt; Cái thấp / Trung cấp kỹ năng &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2408[ Huyền Vũ ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
+    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;2467 1&gt; Chủng loại tính, &lt;2467 1-2&gt; Cái thấp / Trung cấp kỹ năng &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2408[ Huyền Vũ ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
   </si>
   <si>
     <t xml:space="preserve">1.&lt;2405【 Sơ cấp kỹ năng 】&gt;+&lt;2405 【 Sơ cấp kỹ năng 】&gt;&lt;br&gt;2.&lt;2405 【 Sơ cấp kỹ năng 】&gt;+&lt;2405【 Trung cấp kỹ năng 】&gt;&lt;br&gt;3.&lt;2405【 Trung cấp kỹ năng 】&gt;&lt;br&gt;&lt;br&gt; Ngẫu nhiên nhận được trở lên kỹ năng tổ hợp bên trong &lt;2467 1&gt; Loại</t>
@@ -685,7 +685,7 @@
     <t xml:space="preserve">3,2:3000#3,1:3000#2,2:2000#3,2:2000</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;24671&gt; Chủng loại tính, &lt;2467 1-2&gt; Trong đó / Cao cấp kỹ năng &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2409[ Long Tước ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
+    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;2467 1&gt; Chủng loại tính, &lt;2467 1-2&gt; Trong đó / Cao cấp kỹ năng &lt;br&gt; Nhưng tại lò bát quái bên trong hợp thành cao cấp hơn &lt;2409[ Long Tước ấn ]&gt;&lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
   </si>
   <si>
     <t xml:space="preserve">1.&lt;2405【 Trung cấp kỹ năng 】&gt;+&lt;2405 【 Trung cấp kỹ năng 】&gt;&lt;br&gt;2.&lt;2405 【 Cao cấp kỹ năng 】&gt;+&lt;2405【 Sơ cấp kỹ năng 】&gt;&lt;br&gt;3.&lt;2405 【 Cao cấp kỹ năng 】&gt;+&lt;2405【 Trung cấp kỹ năng 】&gt;&lt;br&gt;4.&lt;2405 【 Cao cấp kỹ năng 】&gt;&lt;br&gt;&lt;br&gt; Ngẫu nhiên nhận được trở lên kỹ năng tổ hợp bên trong 1 Loại</t>
@@ -715,7 +715,7 @@
     <t xml:space="preserve">3,3:1000#3,2:9000</t>
   </si>
   <si>
-    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;24672&gt; Chủng loại tính, &lt;2467 2&gt; Trong đó / Cao cấp kỹ năng &lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
+    <t xml:space="preserve">Nhưng ngẫu nhiên nhận được &lt;2467 2&gt; Chủng loại tính, &lt;2467 2&gt; Trong đó / Cao cấp kỹ năng &lt;br&gt; Có vật hỗn thành, tiên thiên sinh, độc lập không thay đổi, Chu Hành không thua</t>
   </si>
   <si>
     <t xml:space="preserve">1.&lt;2405【 Cao cấp kỹ năng 】&gt;+&lt;2405 【 Cao cấp kỹ năng 】&gt;&lt;br&gt;2.&lt;2405 【 Cao cấp kỹ năng 】&gt;+&lt;2405【 Trung cấp kỹ năng 】&gt;&lt;br&gt;&lt;br&gt; Ngẫu nhiên nhận được trở lên kỹ năng tổ hợp bên trong &lt;2467 1&gt; Loại</t>
